--- a/Output/count_num_voxel/Data/Data_num_voxel.xlsx
+++ b/Output/count_num_voxel/Data/Data_num_voxel.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,17 +10,17 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3" documentId="11_F040E617CF19DF4F241D4305F8012D16B1017DBA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13345ADC-25BC-48A8-A15A-B81DD317DE95}"/>
   <bookViews>
-    <workbookView xWindow="470" yWindow="380" windowWidth="10460" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="470" yWindow="380" windowWidth="10460" windowHeight="10300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="33" uniqueCount="17">
   <si>
     <t>Participant_ID</t>
   </si>
@@ -68,13 +68,16 @@
   </si>
   <si>
     <t>lateral ventricles</t>
+  </si>
+  <si>
+    <t>inferior lateral ventricles</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -88,7 +91,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -96,12 +99,14 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -120,7 +125,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -271,7 +276,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -295,9 +300,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -321,7 +326,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -356,7 +361,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -374,7 +379,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -399,7 +404,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -435,234 +440,270 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.90625" customWidth="1"/>
-    <col min="2" max="4" width="6.90625" customWidth="1"/>
-    <col min="5" max="5" width="13.08984375" customWidth="1"/>
-    <col min="6" max="6" width="14.54296875" customWidth="1"/>
+    <col min="1" max="1" width="14.90625" customWidth="true"/>
+    <col min="2" max="2" width="6.90625" customWidth="true"/>
+    <col min="5" max="5" width="13.08984375" customWidth="true"/>
+    <col min="6" max="6" width="14.54296875" customWidth="true"/>
+    <col min="3" max="3" width="6.90625" customWidth="true"/>
+    <col min="4" max="4" width="6.90625" customWidth="true"/>
+    <col min="7" max="7" width="21.1796875" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="G1" s="0" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.35">
+      <c r="A2" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>486027</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>377572</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <v>184501</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="0">
         <v>1033</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="0">
         <v>16055</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="G2" s="0">
+        <v>877</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.35">
+      <c r="A3" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0">
         <v>613861</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0">
         <v>463708</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="0">
         <v>138958</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="0">
         <v>1131</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="0">
         <v>10847</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="G3" s="0">
+        <v>995</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.35">
+      <c r="A4" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0">
         <v>636072</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0">
         <v>392992</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="0">
         <v>176958</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="0">
         <v>1361</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="0">
         <v>24561</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="G4" s="0">
+        <v>1032</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.35">
+      <c r="A5" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0">
         <v>559003</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="0">
         <v>408963</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="0">
         <v>207991</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="0">
         <v>1324</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="0">
         <v>23100</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="G5" s="0">
+        <v>828</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.35">
+      <c r="A6" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0">
         <v>641817</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0">
         <v>438088</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="0">
         <v>190561</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="0">
         <v>2138</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="0">
         <v>40218</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="G6" s="0">
+        <v>1341</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.35">
+      <c r="A7" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0">
         <v>490431</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="0">
         <v>413759</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="0">
         <v>275104</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="0">
         <v>1614</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="0">
         <v>37124</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="G7" s="0">
+        <v>2357</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.35">
+      <c r="A8" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0">
         <v>488651</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="0">
         <v>385360</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="0">
         <v>310273</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="0">
         <v>1464</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="0">
         <v>49156</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="G8" s="0">
+        <v>3263</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.35">
+      <c r="A9" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="0">
         <v>539210</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="0">
         <v>434754</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="0">
         <v>301592</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="0">
         <v>2220</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="0">
         <v>60608</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="G9" s="0">
+        <v>4497</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.35">
+      <c r="A10" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="0">
         <v>511082</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="0">
         <v>365897</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="0">
         <v>330766</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="0">
         <v>1341</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="0">
         <v>85667</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="G10" s="0">
+        <v>3136</v>
+      </c>
+    </row>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.35">
+      <c r="A11" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="0">
         <v>528379</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="0">
         <v>357749</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="0">
         <v>264890</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="0">
         <v>1399</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="0">
         <v>25857</v>
+      </c>
+      <c r="G11" s="0">
+        <v>1052</v>
       </c>
     </row>
   </sheetData>
